--- a/Personal_2024_soc_taxi.xlsx
+++ b/Personal_2024_soc_taxi.xlsx
@@ -564,7 +564,7 @@
         <v>631098.0600000001</v>
       </c>
       <c r="H4" t="n">
-        <v>246128.2434</v>
+        <v>198795.8889</v>
       </c>
     </row>
     <row r="5">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.78</v>
+        <v>0.63</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         <v>577260</v>
       </c>
       <c r="H7" t="n">
-        <v>450262.8</v>
+        <v>363673.8</v>
       </c>
     </row>
     <row r="8">
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.78</v>
+        <v>0.63</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>610576.66</v>
       </c>
       <c r="H14" t="n">
-        <v>476249.7948</v>
+        <v>384663.2958</v>
       </c>
     </row>
     <row r="15">
@@ -899,7 +899,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.78</v>
+        <v>0.63</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>25121.5</v>
       </c>
       <c r="H15" t="n">
-        <v>19594.77</v>
+        <v>15826.545</v>
       </c>
     </row>
     <row r="16">
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.78</v>
+        <v>0.63</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
         <v>577260</v>
       </c>
       <c r="H23" t="n">
-        <v>450262.8</v>
+        <v>363673.8</v>
       </c>
     </row>
     <row r="24">
@@ -1347,7 +1347,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.78</v>
+        <v>0.63</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>577260</v>
       </c>
       <c r="H29" t="n">
-        <v>450262.8</v>
+        <v>363673.8</v>
       </c>
     </row>
     <row r="30">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>246128.2434</v>
+        <v>198795.8889</v>
       </c>
     </row>
     <row r="7">
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1846632.9648</v>
+        <v>1491511.2408</v>
       </c>
     </row>
     <row r="8">
@@ -1758,7 +1758,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5426448.7482</v>
+        <v>5023994.6697</v>
       </c>
     </row>
   </sheetData>
